--- a/FisicaEx02/refs/medidas_fisicaEX02.xlsx
+++ b/FisicaEx02/refs/medidas_fisicaEX02.xlsx
@@ -617,7 +617,7 @@
       <x:c r="E16" s="1"/>
       <x:c r="F16" s="1"/>
       <x:c r="G16" s="1" t="str">
-        <x:v>Foto: dados/foto_medidas_2026-09-29.jpg</x:v>
+        <x:v>Foto: refs/foto_medidas_2026-09-29.jpg</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="24" customHeight="1">
